--- a/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
+++ b/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
@@ -645,9 +645,21 @@
       <c r="F6" t="n">
         <v>0.0336337887017137</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>129229398</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GO:0005764 [Name: lysosome]; GO:0051603 [Name: proteolysis involved in cellular protein catabolic process]; GO:0004197 [Name: cysteine-type endopeptidase activity]; GO:0005615 [Name: extracellular space]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>procathepsin L-like</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>cathepsin L-like peptidase</t>
@@ -677,7 +689,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>129218775</t>
+          <t>129230408</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -687,7 +699,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>piggyBac transposable element-derived protein 4-like</t>
+          <t>uncharacterized LOC129230408</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -923,12 +935,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>129218682</t>
+          <t>129218395</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>GO:0004499 [Name: N,N-dimethylaniline monooxygenase activity]; GO:0050660 [Name: flavin adenine dinucleotide binding]; GO:0050661 [Name: NADP binding]</t>
+          <t>GO:0050661 [Name: NADP binding]; GO:0004499 [Name: N,N-dimethylaniline monooxygenase activity]; GO:0050660 [Name: flavin adenine dinucleotide binding]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5045,12 +5057,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>129217091</t>
+          <t>129216859</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>GO:0004084 [Name: branched-chain-amino-acid transaminase activity]; GO:0005739 [Name: mitochondrion]; GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]</t>
+          <t>GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]; GO:0005739 [Name: mitochondrion]; GO:0004084 [Name: branched-chain-amino-acid transaminase activity]</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5513,12 +5525,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>129218840</t>
+          <t>129225077</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>GO:0000723 [Name: telomere maintenance]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -5783,12 +5795,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>129216597</t>
+          <t>129216599</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>GO:0005829 [Name: cytosol]; GO:0030729 [Name: acetoacetate-CoA ligase activity]; GO:0006629 [Name: lipid metabolic process]</t>
+          <t>GO:0005829 [Name: cytosol]; GO:0030729 [Name: acetoacetate-CoA ligase activity]</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6503,7 +6515,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>129221287</t>
+          <t>129219806</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7223,17 +7235,17 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>129221379</t>
+          <t>129221043</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>GO:0005730 [Name: nucleolus]; GO:0000463 [Name: maturation of LSU-rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]; GO:0000466 [Name: maturation of 5.8S rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]</t>
+          <t>GO:0000466 [Name: maturation of 5.8S rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]; GO:0005730 [Name: nucleolus]; GO:0000463 [Name: maturation of LSU-rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129221379</t>
+          <t>nucleolar pre-ribosomal-associated protein 1-like</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -7389,9 +7401,21 @@
       <c r="F182" t="n">
         <v>0.0068314506529897</v>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
-      <c r="I182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>129219708</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>GO:0071004 [Name: U2-type prespliceosome]; GO:0003729 [Name: mRNA binding]; GO:0005685 [Name: U1 snRNP]; GO:0030619 [Name: U1 snRNA binding]; GO:0000398 [Name: mRNA splicing, via spliceosome]; GO:0071011 [Name: precatalytic spliceosome]</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>small ribonucleoprotein particle U1 subunit 70K</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>U1 small nuclear ribonucleoprotein 70 kDa</t>
@@ -7547,17 +7571,17 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>129230397</t>
+          <t>129230395</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0009395 [Name: phospholipid catabolic process]; GO:0005509 [Name: calcium ion binding]; GO:0004435 [Name: phosphatidylinositol phospholipase C activity]; GO:0005515 [Name: protein binding]; GO:0010634 [Name: positive regulation of epithelial cell migration]</t>
+          <t>GO:0005509 [Name: calcium ion binding]; GO:0004435 [Name: phosphatidylinositol phospholipase C activity]; GO:0005515 [Name: protein binding]; GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0006629 [Name: lipid metabolic process]; GO:0010634 [Name: positive regulation of epithelial cell migration]</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>small wing phospholipase C gamma 1</t>
+          <t>1-phosphatidylinositol 4,5-bisphosphate phosphodiesterase gamma-1-like</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -7787,12 +7811,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>129218572</t>
+          <t>129219115</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>GO:0035567 [Name: non-canonical Wnt signaling pathway]; GO:0060070 [Name: canonical Wnt signaling pathway]; GO:0017147 [Name: Wnt-protein binding]; GO:0005886 [Name: plasma membrane]; GO:0042813 [Name: Wnt-activated receptor activity]</t>
+          <t>GO:0060070 [Name: canonical Wnt signaling pathway]; GO:0035567 [Name: non-canonical Wnt signaling pathway]; GO:0017147 [Name: Wnt-protein binding]; GO:0042813 [Name: Wnt-activated receptor activity]; GO:0005886 [Name: plasma membrane]</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -7943,7 +7967,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>129227279</t>
+          <t>129227546</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8789,12 +8813,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>129227533</t>
+          <t>129218983</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>GO:0005634 [Name: nucleus]; GO:0051726 [Name: regulation of cell cycle]; GO:0043066 [Name: negative regulation of apoptotic process]</t>
+          <t>GO:0043066 [Name: negative regulation of apoptotic process]; GO:0005634 [Name: nucleus]; GO:0051726 [Name: regulation of cell cycle]</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10523,17 +10547,17 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>129220299</t>
+          <t>129220298</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>GO:0012505 [Name: endomembrane system]; GO:0070072 [Name: vacuolar proton-transporting V-type ATPase complex assembly]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0031011 [Name: Ino80 complex]; GO:0006338 [Name: chromatin remodeling]</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>transmembrane protein 199-like</t>
+          <t>uncharacterized LOC129220298</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -10791,9 +10815,21 @@
       <c r="F271" t="n">
         <v>0.0205269797383047</v>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>129232587</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>GO:0043023 [Name: ribosomal large subunit binding]; GO:1990112 [Name: RQC complex]; GO:0008270 [Name: zinc ion binding]; GO:1990116 [Name: ribosome-associated ubiquitin-dependent protein catabolic process]; GO:0005829 [Name: cytosol]; GO:0072344 [Name: rescue of stalled ribosome]; GO:0061630 [Name: ubiquitin protein ligase activity]</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>E3 ubiquitin-protein ligase listerin-like</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr">
         <is>
           <t>E3 ubiquitin-protein ligase listerin</t>
@@ -10821,9 +10857,21 @@
       <c r="F272" t="n">
         <v>0.0236567411223488</v>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
-      <c r="I272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>129217769</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>trichohyalin-like</t>
+        </is>
+      </c>
       <c r="J272" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
@@ -10851,21 +10899,9 @@
       <c r="F273" t="n">
         <v>0.0292081014091282</v>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>129219403</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>GO:0005654 [Name: nucleoplasm]; GO:0000122 [Name: negative regulation of transcription from RNA polymerase II promoter]; GO:0003714 [Name: transcription corepressor activity]; GO:0042826 [Name: histone deacetylase binding]</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>mesoderm induction early response protein 1-like</t>
-        </is>
-      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>mesoderm induction early response protein 1 isoform X7</t>
@@ -12059,7 +12095,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>129220381</t>
+          <t>129220275</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -12101,12 +12137,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>129225878</t>
+          <t>129226297</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>GO:0000995 [Name: transcription factor activity, core RNA polymerase III binding]; GO:0097550 [Name: transcriptional preinitiation complex]; GO:0006352 [Name: DNA-templated transcription, initiation]; GO:0017025 [Name: TBP-class protein binding]; GO:0005634 [Name: nucleus]; GO:0006383 [Name: transcription from RNA polymerase III promoter]; GO:0070897 [Name: DNA-templated transcriptional preinitiation complex assembly]; GO:0001006 [Name: RNA polymerase III type 3 promoter sequence-specific DNA binding]; GO:0000126 [Name: transcription factor TFIIIB complex]</t>
+          <t>GO:0000126 [Name: transcription factor TFIIIB complex]; GO:0097550 [Name: transcriptional preinitiation complex]; GO:0005634 [Name: nucleus]; GO:0070897 [Name: DNA-templated transcriptional preinitiation complex assembly]; GO:0000995 [Name: transcription factor activity, core RNA polymerase III binding]; GO:0006383 [Name: transcription from RNA polymerase III promoter]; GO:0017025 [Name: TBP-class protein binding]; GO:0006352 [Name: DNA-templated transcription, initiation]; GO:0001006 [Name: RNA polymerase III type 3 promoter sequence-specific DNA binding]</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12903,21 +12939,9 @@
       <c r="F327" t="n">
         <v>0.0020240408061473</v>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>129230277</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>GO:0005793 [Name: endoplasmic reticulum-Golgi intermediate compartment]; GO:0005537 [Name: mannose binding]; GO:0000139 [Name: Golgi membrane]; GO:0030134 [Name: ER to Golgi transport vesicle]; GO:0005789 [Name: endoplasmic reticulum membrane]; GO:0006888 [Name: ER to Golgi vesicle-mediated transport]; GO:0007030 [Name: Golgi organization]; GO:0007029 [Name: endoplasmic reticulum organization]</t>
-        </is>
-      </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>VIP36-like protein</t>
-        </is>
-      </c>
+      <c r="G327" t="inlineStr"/>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>VIP36-like protein isoform X2</t>
@@ -13583,7 +13607,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>129222215</t>
+          <t>129224972</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -13593,7 +13617,7 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>histidine-rich glycoprotein-like</t>
+          <t>filaggrin-like</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
@@ -14189,17 +14213,17 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>129224060</t>
+          <t>129224059</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]; GO:0016853 [Name: isomerase activity]</t>
+          <t>GO:0016853 [Name: isomerase activity]; GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224060</t>
+          <t>uncharacterized LOC129224059</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -14315,7 +14339,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>129215989</t>
+          <t>129216478</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -14325,7 +14349,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>pantetheinase-like</t>
+          <t>glutathione S-transferase C-terminal domain-containing protein homolog</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -16757,17 +16781,17 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>129225669</t>
+          <t>129225658</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>GO:0016787 [Name: hydrolase activity]; GO:0005737 [Name: cytoplasm]; GO:0019748 [Name: secondary metabolic process]; GO:0016831 [Name: carboxy-lyase activity]; GO:0005829 [Name: cytosol]</t>
+          <t>GO:0005525 [Name: GTP binding]; GO:0003924 [Name: GTPase activity]; GO:0005739 [Name: mitochondrion]; GO:0000287 [Name: magnesium ion binding]</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>2-amino-3-carboxymuconate-6-semialdehyde decarboxylase-like</t>
+          <t>GTP-binding protein 10-like</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -20525,17 +20549,17 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>129228572</t>
+          <t>129227712</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129228572</t>
+          <t>uncharacterized LOC129227712</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -22197,21 +22221,9 @@
       <c r="F558" t="n">
         <v>0.0193707987169792</v>
       </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>129229285</t>
-        </is>
-      </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>GO:0008137 [Name: NADH dehydrogenase (ubiquinone) activity]; GO:0010181 [Name: FMN binding]; GO:0051287 [Name: NAD binding]; GO:0051539 [Name: 4 iron, 4 sulfur cluster binding]; GO:0006120 [Name: mitochondrial electron transport, NADH to ubiquinone]</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>NADH dehydrogenase [ubiquinone] flavoprotein 1, mitochondrial-like</t>
-        </is>
-      </c>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
       <c r="J558" t="inlineStr">
         <is>
           <t>NADH dehydrogenase [ubiquinone</t>
@@ -28521,21 +28533,9 @@
       <c r="F714" t="n">
         <v>0.0188498660122874</v>
       </c>
-      <c r="G714" t="inlineStr">
-        <is>
-          <t>129228553</t>
-        </is>
-      </c>
-      <c r="H714" t="inlineStr">
-        <is>
-          <t>GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0003676 [Name: nucleic acid binding]; GO:0031213 [Name: RSF complex]</t>
-        </is>
-      </c>
-      <c r="I714" t="inlineStr">
-        <is>
-          <t>histone-lysine N-methyltransferase SETD1B-like</t>
-        </is>
-      </c>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
       <c r="J714" t="inlineStr">
         <is>
           <t>microtubule-associated protein futsch</t>
@@ -29151,9 +29151,21 @@
       <c r="F729" t="n">
         <v>0.0302506589022171</v>
       </c>
-      <c r="G729" t="inlineStr"/>
-      <c r="H729" t="inlineStr"/>
-      <c r="I729" t="inlineStr"/>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>129219454</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>cuticlin-1-like</t>
+        </is>
+      </c>
       <c r="J729" t="inlineStr">
         <is>
           <t>uncharacterized protein</t>
@@ -29633,17 +29645,17 @@
       </c>
       <c r="G741" t="inlineStr">
         <is>
-          <t>129217289</t>
+          <t>129217288</t>
         </is>
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>GO:0005686 [Name: U2 snRNP]; GO:0000398 [Name: mRNA splicing, via spliceosome]; GO:0071011 [Name: precatalytic spliceosome]; GO:0071013 [Name: catalytic step 2 spliceosome]; GO:0005689 [Name: U12-type spliceosomal complex]</t>
+          <t>GO:0001510 [Name: RNA methylation]; GO:0005739 [Name: mitochondrion]; GO:0008650 [Name: rRNA (uridine-2'-O-)-methyltransferase activity]</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>PHD finger protein 5a</t>
+          <t>Mitochondrial rRNA methyltransferase 2</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
@@ -32679,21 +32691,9 @@
       <c r="F817" t="n">
         <v>0.0001000560411034</v>
       </c>
-      <c r="G817" t="inlineStr">
-        <is>
-          <t>129231758</t>
-        </is>
-      </c>
-      <c r="H817" t="inlineStr">
-        <is>
-          <t>GO:0005730 [Name: nucleolus]</t>
-        </is>
-      </c>
-      <c r="I817" t="inlineStr">
-        <is>
-          <t>coiled-coil domain-containing protein 86-like</t>
-        </is>
-      </c>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr"/>
       <c r="J817" t="inlineStr">
         <is>
           <t>coiled-coil domain-containing protein 86</t>

--- a/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
+++ b/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
@@ -645,21 +645,9 @@
       <c r="F6" t="n">
         <v>0.0336337887017137</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>129229398</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>GO:0005764 [Name: lysosome]; GO:0051603 [Name: proteolysis involved in cellular protein catabolic process]; GO:0004197 [Name: cysteine-type endopeptidase activity]; GO:0005615 [Name: extracellular space]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>procathepsin L-like</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>cathepsin L-like peptidase</t>
@@ -935,12 +923,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>129218395</t>
+          <t>129218682</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>GO:0050661 [Name: NADP binding]; GO:0004499 [Name: N,N-dimethylaniline monooxygenase activity]; GO:0050660 [Name: flavin adenine dinucleotide binding]</t>
+          <t>GO:0004499 [Name: N,N-dimethylaniline monooxygenase activity]; GO:0050660 [Name: flavin adenine dinucleotide binding]; GO:0050661 [Name: NADP binding]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2351,17 +2339,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>129222631</t>
+          <t>129223095</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>GO:0043231 [Name: intracellular membrane-bounded organelle]; GO:0020037 [Name: heme binding]; GO:0016712 [Name: oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen]; GO:0005506 [Name: iron ion binding]; GO:0006082 [Name: organic acid metabolic process]; GO:0006805 [Name: xenobiotic metabolic process]; GO:0005737 [Name: cytoplasm]</t>
+          <t>GO:0005737 [Name: cytoplasm]; GO:0016712 [Name: oxidoreductase activity, acting on paired donors, with incorporation or reduction of molecular oxygen, reduced flavin or flavoprotein as one donor, and incorporation of one atom of oxygen]; GO:0020037 [Name: heme binding]; GO:0043231 [Name: intracellular membrane-bounded organelle]; GO:0005506 [Name: iron ion binding]; GO:0006082 [Name: organic acid metabolic process]; GO:0006805 [Name: xenobiotic metabolic process]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>cytochrome P450 2C44-like</t>
+          <t>uncharacterized LOC129223095</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2393,17 +2381,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>129222186</t>
+          <t>129222214</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>GO:0000177 [Name: cytoplasmic exosome (RNase complex)]; GO:0034473 [Name: U1 snRNA 3'-end processing]; GO:0071028 [Name: nuclear mRNA surveillance]; GO:0034475 [Name: U4 snRNA 3'-end processing]; GO:0071042 [Name: nuclear polyadenylation-dependent mRNA catabolic process]; GO:0000467 [Name: exonucleolytic trimming to generate mature 3'-end of 5.8S rRNA from tricistronic rRNA transcript (SSU-rRNA, 5.8S rRNA, LSU-rRNA)]; GO:0034476 [Name: U5 snRNA 3'-end processing]; GO:0000176 [Name: nuclear exosome (RNase complex)]; GO:0071035 [Name: nuclear polyadenylation-dependent rRNA catabolic process]; GO:0071038 [Name: nuclear polyadenylation-dependent tRNA catabolic process]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>exosome complex component Rrp42</t>
+          <t>uncharacterized LOC129222214</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5057,12 +5045,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>129216859</t>
+          <t>129217091</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]; GO:0005739 [Name: mitochondrion]; GO:0004084 [Name: branched-chain-amino-acid transaminase activity]</t>
+          <t>GO:0004084 [Name: branched-chain-amino-acid transaminase activity]; GO:0005739 [Name: mitochondrion]; GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6135,21 +6123,9 @@
       <c r="F151" t="n">
         <v>0.029381107407523</v>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>129220555</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>GO:0042734 [Name: presynaptic membrane]; GO:0005330 [Name: dopamine:sodium symporter activity]; GO:0015874 [Name: norepinephrine transport]; GO:0043005 [Name: neuron projection]; GO:0051583 [Name: dopamine uptake involved in synaptic transmission]; GO:0032809 [Name: neuronal cell body membrane]; GO:0035725 [Name: sodium ion transmembrane transport]</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>sodium-dependent noradrenaline transporter-like</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>sodium- and chloride-dependent glycine transporter 1 isoform X1</t>
@@ -6515,7 +6491,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>129219806</t>
+          <t>129221287</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6965,12 +6941,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>129227225</t>
+          <t>129232958</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>GO:0005525 [Name: GTP binding]; GO:0003924 [Name: GTPase activity]; GO:0005509 [Name: calcium ion binding]</t>
+          <t>GO:0003924 [Name: GTPase activity]; GO:0005525 [Name: GTP binding]</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7361,12 +7337,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>129230592</t>
+          <t>129230594</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>GO:0006750 [Name: glutathione biosynthetic process]; GO:0004363 [Name: glutathione synthase activity]; GO:0005524 [Name: ATP binding]; GO:0005829 [Name: cytosol]; GO:0043295 [Name: glutathione binding]</t>
+          <t>GO:0004363 [Name: glutathione synthase activity]; GO:0005829 [Name: cytosol]; GO:0043295 [Name: glutathione binding]; GO:0006750 [Name: glutathione biosynthetic process]; GO:0005524 [Name: ATP binding]</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7401,21 +7377,9 @@
       <c r="F182" t="n">
         <v>0.0068314506529897</v>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>129219708</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>GO:0071004 [Name: U2-type prespliceosome]; GO:0003729 [Name: mRNA binding]; GO:0005685 [Name: U1 snRNP]; GO:0030619 [Name: U1 snRNA binding]; GO:0000398 [Name: mRNA splicing, via spliceosome]; GO:0071011 [Name: precatalytic spliceosome]</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>small ribonucleoprotein particle U1 subunit 70K</t>
-        </is>
-      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
           <t>U1 small nuclear ribonucleoprotein 70 kDa</t>
@@ -7571,17 +7535,17 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>129230395</t>
+          <t>129230397</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>GO:0005509 [Name: calcium ion binding]; GO:0004435 [Name: phosphatidylinositol phospholipase C activity]; GO:0005515 [Name: protein binding]; GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0006629 [Name: lipid metabolic process]; GO:0010634 [Name: positive regulation of epithelial cell migration]</t>
+          <t>GO:0048015 [Name: phosphatidylinositol-mediated signaling]; GO:0009395 [Name: phospholipid catabolic process]; GO:0005509 [Name: calcium ion binding]; GO:0004435 [Name: phosphatidylinositol phospholipase C activity]; GO:0005515 [Name: protein binding]; GO:0010634 [Name: positive regulation of epithelial cell migration]</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1-phosphatidylinositol 4,5-bisphosphate phosphodiesterase gamma-1-like</t>
+          <t>small wing phospholipase C gamma 1</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -8813,12 +8777,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>129218983</t>
+          <t>129227533</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>GO:0043066 [Name: negative regulation of apoptotic process]; GO:0005634 [Name: nucleus]; GO:0051726 [Name: regulation of cell cycle]</t>
+          <t>GO:0005634 [Name: nucleus]; GO:0051726 [Name: regulation of cell cycle]; GO:0043066 [Name: negative regulation of apoptotic process]</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -11309,17 +11273,17 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>129232083</t>
+          <t>129225302</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>GO:0003755 [Name: peptidyl-prolyl cis-trans isomerase activity]; GO:0005515 [Name: protein binding]</t>
+          <t>GO:0036297 [Name: interstrand cross-link repair]; GO:0043240 [Name: Fanconi anaemia nuclear complex]</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>peptidyl-prolyl cis-trans isomerase FKBP4-like</t>
+          <t>uncharacterized LOC129225302</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -11855,12 +11819,12 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>129220713</t>
+          <t>129234497</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>GO:0042781 [Name: 3'-tRNA processing endoribonuclease activity]; GO:0005739 [Name: mitochondrion]; GO:1990180 [Name: mitochondrial tRNA 3'-end processing]</t>
+          <t>GO:1990180 [Name: mitochondrial tRNA 3'-end processing]; GO:0005739 [Name: mitochondrion]; GO:0042781 [Name: 3'-tRNA processing endoribonuclease activity]</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -12137,12 +12101,12 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>129226297</t>
+          <t>129225878</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>GO:0000126 [Name: transcription factor TFIIIB complex]; GO:0097550 [Name: transcriptional preinitiation complex]; GO:0005634 [Name: nucleus]; GO:0070897 [Name: DNA-templated transcriptional preinitiation complex assembly]; GO:0000995 [Name: transcription factor activity, core RNA polymerase III binding]; GO:0006383 [Name: transcription from RNA polymerase III promoter]; GO:0017025 [Name: TBP-class protein binding]; GO:0006352 [Name: DNA-templated transcription, initiation]; GO:0001006 [Name: RNA polymerase III type 3 promoter sequence-specific DNA binding]</t>
+          <t>GO:0000995 [Name: transcription factor activity, core RNA polymerase III binding]; GO:0097550 [Name: transcriptional preinitiation complex]; GO:0006352 [Name: DNA-templated transcription, initiation]; GO:0017025 [Name: TBP-class protein binding]; GO:0005634 [Name: nucleus]; GO:0006383 [Name: transcription from RNA polymerase III promoter]; GO:0070897 [Name: DNA-templated transcriptional preinitiation complex assembly]; GO:0001006 [Name: RNA polymerase III type 3 promoter sequence-specific DNA binding]; GO:0000126 [Name: transcription factor TFIIIB complex]</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -16781,17 +16745,17 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>129225658</t>
+          <t>129225669</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>GO:0005525 [Name: GTP binding]; GO:0003924 [Name: GTPase activity]; GO:0005739 [Name: mitochondrion]; GO:0000287 [Name: magnesium ion binding]</t>
+          <t>GO:0016787 [Name: hydrolase activity]; GO:0005737 [Name: cytoplasm]; GO:0019748 [Name: secondary metabolic process]; GO:0016831 [Name: carboxy-lyase activity]; GO:0005829 [Name: cytosol]</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>GTP-binding protein 10-like</t>
+          <t>2-amino-3-carboxymuconate-6-semialdehyde decarboxylase-like</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -20549,17 +20513,17 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>129227712</t>
+          <t>129228572</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>GO:0006364 [Name: rRNA processing]; GO:0005634 [Name: nucleus]</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129227712</t>
+          <t>uncharacterized LOC129228572</t>
         </is>
       </c>
       <c r="J517" t="inlineStr">
@@ -22221,9 +22185,21 @@
       <c r="F558" t="n">
         <v>0.0193707987169792</v>
       </c>
-      <c r="G558" t="inlineStr"/>
-      <c r="H558" t="inlineStr"/>
-      <c r="I558" t="inlineStr"/>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>129229285</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>GO:0008137 [Name: NADH dehydrogenase (ubiquinone) activity]; GO:0010181 [Name: FMN binding]; GO:0051287 [Name: NAD binding]; GO:0051539 [Name: 4 iron, 4 sulfur cluster binding]; GO:0006120 [Name: mitochondrial electron transport, NADH to ubiquinone]</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>NADH dehydrogenase [ubiquinone] flavoprotein 1, mitochondrial-like</t>
+        </is>
+      </c>
       <c r="J558" t="inlineStr">
         <is>
           <t>NADH dehydrogenase [ubiquinone</t>
@@ -28533,9 +28509,21 @@
       <c r="F714" t="n">
         <v>0.0188498660122874</v>
       </c>
-      <c r="G714" t="inlineStr"/>
-      <c r="H714" t="inlineStr"/>
-      <c r="I714" t="inlineStr"/>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>129228553</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>GO:0006355 [Name: regulation of transcription, DNA-templated]; GO:0003676 [Name: nucleic acid binding]; GO:0031213 [Name: RSF complex]</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>histone-lysine N-methyltransferase SETD1B-like</t>
+        </is>
+      </c>
       <c r="J714" t="inlineStr">
         <is>
           <t>microtubule-associated protein futsch</t>

--- a/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
+++ b/results/Supplementary_Table_7_PhyloGLM_hits.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J338"/>
+  <dimension ref="A1:M338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>P. tepidariorum best BLAST hit for the HOG</t>
+          <t>P. tepidariorum best BLAST hit LOC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>P. tepidariorum best BLAST hit description</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>U. diversus best BLAST hit LOC</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>U. diversus best BLAST hit description</t>
         </is>
       </c>
     </row>
@@ -506,7 +521,22 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
+          <t>LOC107443813</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>electron transfer flavoprotein subunit beta</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -548,7 +578,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>LOC107438264</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>zygotic DNA replication licensing factor mcm3 isoform X2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>LOC129218073</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: zygotic DNA replication licensing factor mcm3-like</t>
         </is>
       </c>
     </row>
@@ -590,7 +635,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>LOC107438798</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>trafficking protein particle complex subunit 4</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>LOC129224240</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>trafficking protein particle complex subunit 4-like</t>
         </is>
       </c>
     </row>
@@ -632,7 +692,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>LOC107454111</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>mitochondrial ribosome-associated GTPase 2</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>LOC129229571</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>mitochondrial ribosome-associated GTPase 2-like</t>
         </is>
       </c>
     </row>
@@ -674,7 +749,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>LOC107442673</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>LOC129223000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129223000</t>
         </is>
       </c>
     </row>
@@ -716,7 +806,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>LOC107436677</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>STING ER exit protein</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>LOC129219977</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>STING ER exit protein-like</t>
         </is>
       </c>
     </row>
@@ -746,7 +851,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>LOC107440148</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>sphingosine kinase 1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>LOC129230005</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sphingosine kinase 1-like</t>
         </is>
       </c>
     </row>
@@ -776,7 +896,22 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
+          <t>LOC107440103</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>probable ATP-dependent RNA helicase DDX5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>LOC129226043</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129226043 isoform X1</t>
         </is>
       </c>
     </row>
@@ -806,7 +941,22 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
+          <t>LOC107455106</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -848,7 +998,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>LOC107442829</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>glyoxylate reductase/hydroxypyruvate reductase</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>LOC129229577</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>glyoxylate reductase/hydroxypyruvate reductase-like</t>
         </is>
       </c>
     </row>
@@ -890,7 +1055,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>LOC107450051</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>acetoacetyl-CoA synthetase isoform X3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>LOC129230105</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>acetoacetyl-CoA synthetase-like</t>
         </is>
       </c>
     </row>
@@ -932,7 +1112,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>LOC107456927</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>neuroguidin</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>LOC129220335</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>neuroguidin-A-like</t>
         </is>
       </c>
     </row>
@@ -974,7 +1169,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>LOC107446924</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>F-box only protein 7 isoform X2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>LOC129228189</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>F-box only protein 7-like</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1226,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>LOC107451995</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>tetraspanin-18B</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>LOC129227485</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>tetraspanin-18-like</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1283,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>LOC107446745</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>small ribosomal subunit protein uS9m</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>LOC129227763</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>28S ribosomal protein S9, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1328,22 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
+          <t>LOC107446889</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>major facilitator superfamily domain-containing protein 6</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>LOC129223906</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129223906</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1385,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>LOC107449921</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>LOC129220392</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129220392</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1442,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>LOC107445002</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>afadin- and alpha-actinin-binding protein A</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>LOC129224844</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>afadin- and alpha-actinin-binding protein A-like</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1499,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>LOC107452529</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>peptidyl-glycine alpha-amidating monooxygenase A</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>LOC129216866</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>peptidyl-glycine alpha-amidating monooxygenase B-like</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1556,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>LOC122268389</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>ribonuclease P protein subunit p21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>LOC129234616</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129234616</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1591,7 @@
         <v>6.6913979714677</v>
       </c>
       <c r="E22" t="n">
-        <v>2.21048597278452e-11</v>
+        <v>2.210485972784519e-11</v>
       </c>
       <c r="F22" t="n">
         <v>2.644404369242121e-07</v>
@@ -1298,7 +1613,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>LOC107442218</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>grpE protein homolog, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>LOC129222444</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>grpE protein homolog, mitochondrial-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1670,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>LOC107453950</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>aquaporin AQPAe.a-like isoform X2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>LOC129222872</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: aquaporin AQPAe.a-like</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1708,7 @@
         <v>3.15626959393102e-11</v>
       </c>
       <c r="F24" t="n">
-        <v>3.77584531521968e-07</v>
+        <v>3.775845315219678e-07</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1382,7 +1727,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>LOC107449952</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>protein YIPF6</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>LOC129228309</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>protein YIPF6-like</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1784,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>LOC107448052</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>small ribosomal subunit protein mS25</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>LOC129225913</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: probable 28S ribosomal protein S25, mitochondrial</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1841,22 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>LOC107444215</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>ras association domain-containing protein 8 isoform X1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>LOC129222008</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>ras association domain-containing protein 8-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1898,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>LOC107452314</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>EEF1A lysine methyltransferase 1</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>LOC129224394</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>EEF1A lysine methyltransferase 1-like</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1955,22 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>LOC107444184</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>peptidyl-prolyl cis-trans isomerase H</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>LOC129217241</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>peptidyl-prolyl cis-trans isomerase H-like</t>
         </is>
       </c>
     </row>
@@ -1592,7 +2012,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>LOC107447083</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>RING-box protein 2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>LOC129222389</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>RING-box protein 2-like</t>
         </is>
       </c>
     </row>
@@ -1634,6 +2069,21 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>LOC107443816</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>NADH dehydrogenase [ubiquinone</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LOC129224459</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>NADH dehydrogenase [ubiquinone</t>
         </is>
       </c>
@@ -1676,7 +2126,22 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>LOC107436786</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>deoxyhypusine hydroxylase</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>LOC129226194</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>deoxyhypusine hydroxylase-like</t>
         </is>
       </c>
     </row>
@@ -1718,7 +2183,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>LOC107454054</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>nucleolar protein 16</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>LOC129229496</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>nucleolar protein 16-like</t>
         </is>
       </c>
     </row>
@@ -1760,7 +2240,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>LOC107455120</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>charged multivesicular body protein 3</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>LOC129231478</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>charged multivesicular body protein 3-like</t>
         </is>
       </c>
     </row>
@@ -1802,7 +2297,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>LOC107445052</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>LOC129227603</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129227603</t>
         </is>
       </c>
     </row>
@@ -1844,7 +2354,22 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>LOC107441996</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>golgin subfamily A member 5 isoform X1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>LOC129223910</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>golgin subfamily A member 5-like</t>
         </is>
       </c>
     </row>
@@ -1886,7 +2411,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>LOC107450236</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>DNA-dependent metalloprotease dvc-1 isoform X2</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>LOC129216442</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>DNA-dependent metalloprotease SPRTN-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -1919,6 +2459,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1943,12 +2498,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>129217091</t>
+          <t>129216859</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>GO:0004084 [Name: branched-chain-amino-acid transaminase activity]; GO:0005739 [Name: mitochondrion]; GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]</t>
+          <t>GO:0009099 [Name: valine biosynthetic process]; GO:0009098 [Name: leucine biosynthetic process]; GO:0005739 [Name: mitochondrion]; GO:0004084 [Name: branched-chain-amino-acid transaminase activity]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -1958,7 +2513,22 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>LOC107448791</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>branched-chain-amino-acid aminotransferase, cytosolic</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>LOC129217091</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>branched-chain-amino-acid aminotransferase, cytosolic-like</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2570,22 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>LOC107436587</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>terminal nucleotidyltransferase 4B isoform X1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>LOC129229284</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>terminal nucleotidyltransferase 4B-like</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2615,22 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
+          <t>LOC107443532</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>polyhomeotic-proximal chromatin protein</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>LOC129220643</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: polyhomeotic-like protein 2</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2672,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>LOC107446755</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>FAD-linked sulfhydryl oxidase ALR isoform X1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>LOC129220407</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>FAD-linked sulfhydryl oxidase ALR-like</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2729,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>LOC107437625</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>serine/arginine repetitive matrix protein 2</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>LOC129229857</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>protein obstructor-E-like</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2786,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>LOC107456788</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>nuclear receptor-interacting protein 3</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>LOC129222130</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129222130</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2843,22 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>LOC107452506</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>trafficking protein particle complex subunit 6b</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>LOC129222717</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>trafficking protein particle complex subunit 6B-like</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2900,22 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>LOC107440451</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>LOC129216173</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>monocarboxylate transporter 12-B-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2957,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>LOC107440216</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>LOC129229332</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129229332 isoform X1</t>
         </is>
       </c>
     </row>
@@ -2324,7 +3014,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>LOC107444053</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>evolutionarily conserved signaling intermediate in Toll pathway, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>LOC129220464</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>evolutionarily conserved signaling intermediate in Toll pathway, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -2366,7 +3071,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>LOC107457202</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>trafficking protein particle complex subunit 11</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>LOC129235297</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>trafficking protein particle complex subunit 11-like</t>
         </is>
       </c>
     </row>
@@ -2408,7 +3128,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>LOC107439479</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>DNA polymerase kappa isoform X1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>LOC129233907</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>DNA polymerase kappa-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -2450,7 +3185,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>LOC107444621</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>guanine nucleotide-binding protein subunit alpha homolog</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>LOC129227764</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>guanine nucleotide-binding protein subunit alpha-13-like</t>
         </is>
       </c>
     </row>
@@ -2492,7 +3242,22 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>LOC107451213</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>dual specificity protein phosphatase 10</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>LOC129229589</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>dual specificity protein phosphatase 10-like</t>
         </is>
       </c>
     </row>
@@ -2522,7 +3287,22 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
+          <t>LOC107443068</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>mortality factor 4-like protein 1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>LOC129221222</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>mortality factor 4-like protein 1</t>
         </is>
       </c>
     </row>
@@ -2564,7 +3344,22 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>LOC107441739</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>zinc finger protein 511</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>LOC129226074</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>zinc finger protein 511-like</t>
         </is>
       </c>
     </row>
@@ -2606,7 +3401,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>LOC107441834</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>Fanconi anemia core complex-associated protein 24 isoform X1</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>LOC129225230</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Fanconi anemia core complex-associated protein 24-like</t>
         </is>
       </c>
     </row>
@@ -2648,7 +3458,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>LOC107453887</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>translocon-associated protein subunit beta</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LOC129222097</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>translocon-associated protein subunit beta-like</t>
         </is>
       </c>
     </row>
@@ -2675,12 +3500,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>129224446</t>
+          <t>129224445</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>GO:0005886 [Name: plasma membrane]; GO:0005243 [Name: gap junction channel activity]; GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]</t>
+          <t>GO:0005921 [Name: gap junction]; GO:0007602 [Name: phototransduction]; GO:0005886 [Name: plasma membrane]; GO:0005243 [Name: gap junction channel activity]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2690,7 +3515,22 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>LOC107449219</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>innexin inx2</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>LOC129224445</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>innexin inx2-like</t>
         </is>
       </c>
     </row>
@@ -2732,6 +3572,21 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>LOC107455745</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>DNA-directed RNA polymerase III subunit RPC7-like</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>LOC129226566</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
           <t>DNA-directed RNA polymerase III subunit RPC7-like</t>
         </is>
       </c>
@@ -2757,24 +3612,27 @@
       <c r="F58" t="n">
         <v>1.19004709737225e-05</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>129216891</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>GO:0004735 [Name: pyrroline-5-carboxylate reductase activity]; GO:0055129 [Name: L-proline biosynthetic process]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>LOC107452833</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>pyrroline-5-carboxylate reductase 2 isoform X4</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>LOC129216891</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>pyrroline-5-carboxylate reductase 2-like</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>pyrroline-5-carboxylate reductase 2 isoform X4</t>
         </is>
       </c>
     </row>
@@ -2816,7 +3674,22 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>LOC107450009</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>activating signal cointegrator 1 complex subunit 2 isoform X3</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>LOC129228557</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>activating signal cointegrator 1 complex subunit 2-like</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3731,22 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>LOC107455170</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>ER membrane protein complex subunit 3</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>LOC129217629</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ER membrane protein complex subunit 3-like</t>
         </is>
       </c>
     </row>
@@ -2900,7 +3788,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>LOC107439038</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>eukaryotic translation initiation factor 5B</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>LOC129230714</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>eukaryotic translation initiation factor 5B-like</t>
         </is>
       </c>
     </row>
@@ -2942,7 +3845,22 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>LOC107455792</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>cleavage and polyadenylation specificity factor subunit 4</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>LOC129225286</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>cleavage and polyadenylation specificity factor subunit 4-like</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3902,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>LOC107436294</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>2-oxoisovalerate dehydrogenase subunit beta, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>LOC129225566</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2-oxoisovalerate dehydrogenase subunit beta, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -3014,6 +3947,21 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
+          <t>LOC107457574</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>B-cell lymphoma 3 protein homolog</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>LOC129223629</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
           <t>B-cell lymphoma 3 protein homolog</t>
         </is>
       </c>
@@ -3056,7 +4004,22 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>LOC107453590</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>LOC129234162</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129234162</t>
         </is>
       </c>
     </row>
@@ -3098,7 +4061,22 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>LOC107456139</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>LOC129224663</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224663 isoform X1</t>
         </is>
       </c>
     </row>
@@ -3121,7 +4099,7 @@
         <v>1.70856928915914e-09</v>
       </c>
       <c r="F67" t="n">
-        <v>2.04396144062108e-05</v>
+        <v>2.043961440621079e-05</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3140,7 +4118,22 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>LOC107439011</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>B9 domain-containing protein 2</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>LOC129224405</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>B9 domain-containing protein 2-like</t>
         </is>
       </c>
     </row>
@@ -3182,7 +4175,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>LOC107443363</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>proliferation-associated protein 2G4</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>LOC129221653</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>proliferation-associated protein 2G4-like</t>
         </is>
       </c>
     </row>
@@ -3212,7 +4220,22 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
+          <t>LOC107441153</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>protein FAN</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>LOC129216819</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>protein FAN-like</t>
         </is>
       </c>
     </row>
@@ -3254,7 +4277,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t>LOC107456217</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t>GA-binding protein subunit beta-1</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>LOC129235293</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>GA-binding protein subunit beta-1-like</t>
         </is>
       </c>
     </row>
@@ -3299,6 +4337,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>LOC129225944</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>mediator of RNA polymerase II transcription subunit 9-like</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3338,7 +4391,22 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>LOC107455920</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>elongator complex protein 6</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>LOC129226528</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>elongator complex protein 6-like</t>
         </is>
       </c>
     </row>
@@ -3380,7 +4448,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>LOC107455324</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>tribbles homolog 2</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>LOC129219679</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>tribbles homolog 2-like</t>
         </is>
       </c>
     </row>
@@ -3421,6 +4504,21 @@
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>LOC107453621</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>surfeit locus protein 4 homolog</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>LOC129227423</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>surfeit locus protein 4 homolog</t>
         </is>
@@ -3452,7 +4550,22 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
+          <t>LOC107444793</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>tudor and KH domain-containing protein homolog</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>LOC129228518</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129228518</t>
         </is>
       </c>
     </row>
@@ -3494,7 +4607,22 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>LOC107443627</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>LOC129222795</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>CDGSH iron-sulfur domain-containing protein 3, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -3517,7 +4645,7 @@
         <v>3.57647148528599e-09</v>
       </c>
       <c r="F77" t="n">
-        <v>4.278532837847631e-05</v>
+        <v>4.27853283784763e-05</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3536,7 +4664,22 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>LOC107448479</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 97</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>LOC129226288</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>coiled-coil domain-containing protein 97-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -3566,7 +4709,22 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
+          <t>LOC107454763</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>F-box/LRR-repeat protein 14</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>LOC129230433</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>F-box/LRR-repeat protein 14-like</t>
         </is>
       </c>
     </row>
@@ -3596,7 +4754,22 @@
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
+          <t>LOC107442064</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>zinc finger protein 629 isoform X2</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>LOC129219632</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>zinc finger protein 629-like</t>
         </is>
       </c>
     </row>
@@ -3638,7 +4811,22 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>LOC107437076</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>nicotinamide/nicotinic acid mononucleotide adenylyltransferase 1 isoform X2</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>LOC129229653</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>nicotinamide/nicotinic acid mononucleotide adenylyltransferase 1-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -3668,7 +4856,22 @@
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
+          <t>LOC107438935</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>LOC129226234</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>probable 28S rRNA (cytosine(4447)-C(5))-methyltransferase</t>
         </is>
       </c>
     </row>
@@ -3710,7 +4913,22 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>LOC107455001</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>protein LZIC</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>LOC129222003</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>protein LZIC-like</t>
         </is>
       </c>
     </row>
@@ -3730,7 +4948,7 @@
         <v>5.84809755606409</v>
       </c>
       <c r="E83" t="n">
-        <v>4.972269257328849e-09</v>
+        <v>4.97226925732885e-09</v>
       </c>
       <c r="F83" t="n">
         <v>5.948325712542504e-05</v>
@@ -3752,7 +4970,22 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>LOC107442530</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>origin recognition complex subunit 2</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>LOC129227980</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>origin recognition complex subunit 2-like</t>
         </is>
       </c>
     </row>
@@ -3794,7 +5027,22 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>LOC107441734</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>translation initiation factor eIF2B subunit delta</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>LOC129225763</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>translation initiation factor eIF-2B subunit delta-like</t>
         </is>
       </c>
     </row>
@@ -3824,7 +5072,22 @@
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
+          <t>LOC107450459</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>protein Spindly isoform X1</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -3866,7 +5129,22 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>LOC107455529</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>transmembrane protein 115</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>LOC129231147</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>transmembrane protein 115-like</t>
         </is>
       </c>
     </row>
@@ -3896,7 +5174,22 @@
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
+          <t>LOC107452457</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>DNA-directed RNA polymerase III subunit RPC10</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>LOC129228427</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>transcription elongation factor S-II-like</t>
         </is>
       </c>
     </row>
@@ -3926,7 +5219,22 @@
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
+          <t>LOC107441205</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>putative Polycomb group protein ASXL2</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>LOC129220358</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>polycomb protein Asx-like</t>
         </is>
       </c>
     </row>
@@ -3968,7 +5276,22 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>LOC107456694</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>ADP-ribosylation factor-like protein 5B isoform X1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>LOC129234106</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>ADP-ribosylation factor-like protein 5B</t>
         </is>
       </c>
     </row>
@@ -4009,6 +5332,21 @@
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>LOC107453129</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>uncharacterized protein C1orf131 homolog</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>LOC129225153</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t>uncharacterized protein C1orf131 homolog</t>
         </is>
@@ -4040,7 +5378,22 @@
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
+          <t>LOC107444888</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>protein phosphatase 1 regulatory subunit 14B isoform X2</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>LOC129227543</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>protein phosphatase 1 regulatory subunit 14B-like</t>
         </is>
       </c>
     </row>
@@ -4082,7 +5435,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>LOC107438639</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>serine/threonine-protein kinase RIO1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>LOC129229787</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>serine/threonine-protein kinase RIO1-like</t>
         </is>
       </c>
     </row>
@@ -4124,7 +5492,22 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>LOC107438640</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>KRR1 small subunit processome component homolog</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>LOC129230739</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>KRR1 small subunit processome component homolog isoform X1</t>
         </is>
       </c>
     </row>
@@ -4166,7 +5549,22 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t>LOC107438211</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>LOC129221901</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129221901</t>
         </is>
       </c>
     </row>
@@ -4207,6 +5605,21 @@
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>LOC107450550</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>PRKR-interacting protein 1 homolog</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>LOC129217496</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>PRKR-interacting protein 1 homolog</t>
         </is>
@@ -4238,6 +5651,21 @@
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
+          <t>LOC122268219</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>protein KRI1 homolog</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>LOC129227461</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
           <t>protein KRI1 homolog</t>
         </is>
       </c>
@@ -4280,7 +5708,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t>LOC107438565</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t>pre-miRNA 5'-monophosphate methyltransferase</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>LOC129221334</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>pre-miRNA 5'-monophosphate methyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -4322,7 +5765,22 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t>LOC107443902</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t>ataxin-2-like protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>LOC129227472</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>ataxin-2-like protein</t>
         </is>
       </c>
     </row>
@@ -4364,7 +5822,22 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>LOC107453183</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>LOC129216969</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129216969</t>
         </is>
       </c>
     </row>
@@ -4406,7 +5879,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t>LOC107441644</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>glutamic acid-rich protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>LOC129216990</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129216990</t>
         </is>
       </c>
     </row>
@@ -4448,7 +5936,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t>LOC107442226</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t>ubiquitin thioesterase ZRANB1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>LOC129233168</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>ubiquitin thioesterase zranb1-B-like</t>
         </is>
       </c>
     </row>
@@ -4490,7 +5993,22 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t>LOC107442565</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t>large ribosomal subunit protein mL52</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>LOC129229501</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>39S ribosomal protein L52, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -4520,7 +6038,22 @@
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
+          <t>LOC107457317</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t>putative uncharacterized protein DDB_G0292636</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -4562,7 +6095,22 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>LOC107452083</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>LOC129230010</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129230010</t>
         </is>
       </c>
     </row>
@@ -4604,7 +6152,22 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t>LOC107446925</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t>DNA replication complex GINS protein PSF1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>LOC129229298</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>DNA replication complex GINS protein PSF1-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -4646,6 +6209,21 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t>LOC107456267</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>histone-binding protein RBBP4</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>LOC129221853</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
           <t>histone-binding protein RBBP4</t>
         </is>
       </c>
@@ -4688,7 +6266,22 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t>LOC107436318</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t>protein phosphatase 1 regulatory subunit 7 isoform X2</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>LOC129223908</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>protein phosphatase 1 regulatory subunit 7-like</t>
         </is>
       </c>
     </row>
@@ -4730,7 +6323,22 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t>LOC107448604</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t>zinc metalloproteinase nas-4</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>LOC129222820</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>zinc metalloproteinase nas-4-like</t>
         </is>
       </c>
     </row>
@@ -4772,7 +6380,22 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t>LOC122268998</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t>ubiquitin-conjugating enzyme E2 J2 isoform X4</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>LOC129227269</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>ubiquitin-conjugating enzyme E2 J2-like</t>
         </is>
       </c>
     </row>
@@ -4814,7 +6437,22 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t>LOC107441171</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t>proliferating cell nuclear antigen</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>LOC129234183</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>proliferating cell nuclear antigen-like</t>
         </is>
       </c>
     </row>
@@ -4856,7 +6494,22 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t>LOC107436494</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t>palmitoyltransferase ZDHHC6</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>LOC129229504</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>palmitoyltransferase ZDHHC6-like</t>
         </is>
       </c>
     </row>
@@ -4898,7 +6551,22 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t>LOC107449708</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t>tRNA (guanine(37)-N(1))-methyltransferase isoform X3</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>LOC129227519</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>tRNA (guanine(37)-N1)-methyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -4940,7 +6608,22 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t>LOC107453197</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>LOC129224684</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224684</t>
         </is>
       </c>
     </row>
@@ -4982,7 +6665,22 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t>LOC107447543</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t>vesicle-associated membrane protein 7</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>LOC129225259</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>vesicle-associated membrane protein 7-like</t>
         </is>
       </c>
     </row>
@@ -5024,7 +6722,22 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t>LOC107448615</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t>26S proteasome non-ATPase regulatory subunit 9</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>LOC129222076</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>26S proteasome non-ATPase regulatory subunit 9-like</t>
         </is>
       </c>
     </row>
@@ -5066,7 +6779,22 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t>LOC107438906</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t>endoplasmic reticulum resident protein 44 isoform X2</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>LOC129216165</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>endoplasmic reticulum resident protein 44-like</t>
         </is>
       </c>
     </row>
@@ -5108,7 +6836,22 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t>LOC122271722</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t>transmembrane ascorbate-dependent reductase CYB561</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>LOC129225960</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>transmembrane ascorbate-dependent reductase CYB561-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -5150,7 +6893,22 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t>LOC107442400</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>LOC129233250</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>F-box only protein 21-like</t>
         </is>
       </c>
     </row>
@@ -5192,7 +6950,22 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t>LOC107452758</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t>COMM domain-containing protein 4</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>LOC129218394</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>COMM domain-containing protein 4-like</t>
         </is>
       </c>
     </row>
@@ -5234,7 +7007,22 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t>LOC107453598</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t>high affinity copper uptake protein 1</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>LOC129232730</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>high affinity copper uptake protein 1-like</t>
         </is>
       </c>
     </row>
@@ -5276,7 +7064,22 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t>LOC107447242</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t>protein big brother isoform X3</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>LOC129224523</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>protein big brother-like</t>
         </is>
       </c>
     </row>
@@ -5306,7 +7109,22 @@
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
+          <t>LOC107440941</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t>dual specificity protein kinase CLK2 isoform X2</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>LOC129232824</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>pre-mRNA-splicing factor 38B-like</t>
         </is>
       </c>
     </row>
@@ -5348,7 +7166,22 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t>LOC107439443</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t>vesicle-associated membrane protein 7</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>LOC129224540</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224540</t>
         </is>
       </c>
     </row>
@@ -5390,7 +7223,22 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t>LOC107455418</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t>RING finger protein 11</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>LOC129221345</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>RING finger protein 11-like</t>
         </is>
       </c>
     </row>
@@ -5432,7 +7280,22 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t>LOC107457302</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t>zinc finger-containing ubiquitin peptidase 1</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>LOC129228346</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>zinc finger-containing ubiquitin peptidase 1-like</t>
         </is>
       </c>
     </row>
@@ -5474,7 +7337,22 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t>LOC107454164</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t>ceramide-1-phosphate transfer protein</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>LOC129233568</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ceramide-1-phosphate transfer protein-like</t>
         </is>
       </c>
     </row>
@@ -5516,7 +7394,22 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t>LOC107451897</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t>protein-L-histidine N-pros-methyltransferase</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>LOC129229400</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>protein-L-histidine N-pros-methyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -5558,7 +7451,22 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t>LOC107451973</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t>golgin subfamily A member 7</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -5600,7 +7508,22 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t>LOC122268887</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>zinc finger protein 420-like</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>LOC129230748</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gastrula zinc finger protein XlCGF57.1-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -5642,7 +7565,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t>LOC107440345</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t>tyrosine aminotransferase</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>LOC129220189</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: tyrosine aminotransferase-like</t>
         </is>
       </c>
     </row>
@@ -5684,7 +7622,22 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t>LOC107443016</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t>cyclin-dependent kinase 2-interacting protein</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>LOC129221120</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>cyclin-dependent kinase 2-interacting protein-like</t>
         </is>
       </c>
     </row>
@@ -5726,7 +7679,22 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t>LOC107448331</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t>COP9 signalosome complex subunit 8</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>LOC129229469</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>COP9 signalosome complex subunit 8-like</t>
         </is>
       </c>
     </row>
@@ -5768,7 +7736,22 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t>LOC110283246</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>LOC129220262</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129220262</t>
         </is>
       </c>
     </row>
@@ -5798,7 +7781,22 @@
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
+          <t>LOC107448264</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t>membrane-associated protein Hem isoform X2</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>LOC129219117</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>membrane-associated protein Hem-like</t>
         </is>
       </c>
     </row>
@@ -5840,7 +7838,22 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t>LOC107443071</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t>UBX domain-containing protein 7</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>LOC129222395</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: UBX domain-containing protein 7-like</t>
         </is>
       </c>
     </row>
@@ -5882,7 +7895,22 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t>LOC107436732</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t>prohibitin-2 isoform X1</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>LOC129222013</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>prohibitin-2-like</t>
         </is>
       </c>
     </row>
@@ -5915,6 +7943,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5954,7 +7997,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t>LOC107439418</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t>nucleolar protein 56</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>LOC129229276</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>nucleolar protein 56-like</t>
         </is>
       </c>
     </row>
@@ -5996,7 +8054,22 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t>LOC107456583</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t>myophilin</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>LOC129223896</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>myophilin-like</t>
         </is>
       </c>
     </row>
@@ -6038,7 +8111,22 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t>LOC107443731</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t>platelet-activating factor acetylhydrolase IB subunit alpha1</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>LOC129222280</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>platelet-activating factor acetylhydrolase IB subunit alpha1-like</t>
         </is>
       </c>
     </row>
@@ -6080,7 +8168,22 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t>LOC107456293</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t>zinc finger protein 92</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>LOC129233887</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>zinc finger protein 430-like</t>
         </is>
       </c>
     </row>
@@ -6122,7 +8225,22 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t>LOC107447456</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t>corticotropin-releasing factor-binding protein</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>LOC129226015</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>corticotropin-releasing factor-binding protein-like</t>
         </is>
       </c>
     </row>
@@ -6164,6 +8282,21 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t>LOC107437778</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>lissencephaly-1 homolog</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>LOC129221308</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
           <t>lissencephaly-1 homolog</t>
         </is>
       </c>
@@ -6206,7 +8339,22 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t>LOC107453415</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t>ankyrin repeat, SAM and basic leucine zipper domain-containing protein 1</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>LOC129225824</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>ankyrin repeat, SAM and basic leucine zipper domain-containing protein 1-like</t>
         </is>
       </c>
     </row>
@@ -6248,7 +8396,22 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t>LOC107450555</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t>pescadillo homolog</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>LOC129216153</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>pescadillo-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -6290,7 +8453,22 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t>LOC107455562</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 32</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>LOC129228053</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129228053</t>
         </is>
       </c>
     </row>
@@ -6332,6 +8510,21 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t>LOC107455019</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>protein LTO1 homolog</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>LOC129226535</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
           <t>protein LTO1 homolog</t>
         </is>
       </c>
@@ -6374,7 +8567,22 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t>LOC107447085</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t>transmembrane protein 256 homolog</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>LOC129221868</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: transmembrane protein 256 homolog</t>
         </is>
       </c>
     </row>
@@ -6416,7 +8624,22 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t>LOC107444216</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>LOC129222148</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129222148</t>
         </is>
       </c>
     </row>
@@ -6458,7 +8681,22 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t>LOC107436197</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 174 isoform X1</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>LOC129217038</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>coiled-coil domain-containing protein 174-like</t>
         </is>
       </c>
     </row>
@@ -6500,7 +8738,22 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t>LOC107443881</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t>insulin-induced gene 1 protein</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>LOC129225304</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>insulin-induced gene 2 protein-like</t>
         </is>
       </c>
     </row>
@@ -6542,7 +8795,22 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t>LOC107449630</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t>E3 ubiquitin-protein ligase PPP1R11</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>LOC129219659</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>E3 ubiquitin-protein ligase PPP1R11-like</t>
         </is>
       </c>
     </row>
@@ -6584,7 +8852,22 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t>LOC107442957</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t>mRNA-capping enzyme isoform X2</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>LOC129219840</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: mRNA-capping enzyme-like</t>
         </is>
       </c>
     </row>
@@ -6626,7 +8909,22 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t>LOC107436676</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t>large ribosomal subunit protein bL17m</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>LOC129220337</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>39S ribosomal protein L17, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -6668,7 +8966,22 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t>LOC107448319</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t>dnaJ homolog subfamily C member 25 homolog</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>LOC129218060</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>dnaJ homolog subfamily C member 25 homolog isoform X1</t>
         </is>
       </c>
     </row>
@@ -6713,6 +9026,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>LOC129234301</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>GSK3-beta interaction protein-like</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6752,7 +9080,22 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t>LOC107438323</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t>methionine aminopeptidase 1</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>LOC129225709</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>methionine aminopeptidase 1-like</t>
         </is>
       </c>
     </row>
@@ -6794,7 +9137,22 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t>LOC107438994</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t>threonylcarbamoyl-AMP synthase</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>LOC129226380</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>threonylcarbamoyl-AMP synthase-like</t>
         </is>
       </c>
     </row>
@@ -6836,6 +9194,21 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t>LOC107452133</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>coiled-coil domain-containing protein 130 homolog</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>LOC129216860</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 130 homolog</t>
         </is>
       </c>
@@ -6878,7 +9251,22 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t>LOC107436678</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t>centrosomal protein of 41 kDa B isoform X1</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>LOC129219975</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>centrosomal protein of 41 kDa B-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -6920,7 +9308,22 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t>LOC107443267</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t>anamorsin homolog</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>LOC129221583</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>anamorsin homolog isoform X1</t>
         </is>
       </c>
     </row>
@@ -6962,7 +9365,22 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t>LOC107455840</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t>splicing factor C9orf78</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>LOC129222116</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>splicing factor C9orf78-like</t>
         </is>
       </c>
     </row>
@@ -7004,7 +9422,22 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t>LOC107436258</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t>rab-like protein 3</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>LOC129233935</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>rab-like protein 3 isoform X1</t>
         </is>
       </c>
     </row>
@@ -7046,7 +9479,22 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t>LOC107445179</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t>actin-binding Rho-activating protein</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>LOC129217180</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>actin-binding Rho-activating protein-like</t>
         </is>
       </c>
     </row>
@@ -7088,7 +9536,22 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t>LOC107439875</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t>damage-control phosphatase ARMT1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>LOC129221671</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>damage-control phosphatase ARMT1-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -7130,7 +9593,22 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t>LOC107452251</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>LOC129228574</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129228574</t>
         </is>
       </c>
     </row>
@@ -7172,7 +9650,22 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t>LOC107441030</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t>ERI1 exoribonuclease 3 isoform X2</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>LOC129221287</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>ERI1 exoribonuclease 3-like</t>
         </is>
       </c>
     </row>
@@ -7202,7 +9695,22 @@
       <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
+          <t>LOC107457027</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t>prefoldin subunit 6</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -7244,7 +9752,22 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t>LOC107437851</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t>iroquois-class homeodomain protein IRX-6 isoform X3</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>LOC129216138</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>iroquois-class homeodomain protein IRX-6-like</t>
         </is>
       </c>
     </row>
@@ -7274,7 +9797,22 @@
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
+          <t>LOC107436910</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -7304,7 +9842,22 @@
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
+          <t>LOC107457204</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t>protein MIX23</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -7346,7 +9899,22 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t>LOC107451421</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t>influenza virus NS1A-binding protein homolog B isoform X1</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>LOC129223368</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>influenza virus NS1A-binding protein homolog B-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -7388,7 +9956,22 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t>LOC107455768</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t>breast cancer metastasis-suppressor 1-like protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>LOC129225280</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>breast cancer metastasis-suppressor 1-like protein-A isoform X2</t>
         </is>
       </c>
     </row>
@@ -7418,7 +10001,22 @@
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
+          <t>LOC107450633</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t>general receptor for phosphoinositides 1-associated scaffold protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>LOC129230252</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>microtubule-associated serine/threonine-protein kinase 3-like</t>
         </is>
       </c>
     </row>
@@ -7460,7 +10058,22 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t>LOC107442390</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t>multiple myeloma tumor-associated protein 2</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>LOC129226121</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>multiple myeloma tumor-associated protein 2 homolog</t>
         </is>
       </c>
     </row>
@@ -7502,7 +10115,22 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t>LOC107441538</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>LOC129227272</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129227272 isoform X2</t>
         </is>
       </c>
     </row>
@@ -7544,7 +10172,22 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t>LOC110282956</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>LOC129229670</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129229670</t>
         </is>
       </c>
     </row>
@@ -7586,7 +10229,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t>LOC122271367</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t>allatotropins-like isoform X1</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>LOC129221358</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>allatotropins-like</t>
         </is>
       </c>
     </row>
@@ -7616,7 +10274,22 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
+          <t>LOC107456020</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t>CCA tRNA nucleotidyltransferase 1, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>LOC129225642</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>CCA tRNA nucleotidyltransferase 1, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -7658,7 +10331,22 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t>LOC107445488</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t>transforming growth factor-beta receptor-associated protein 1</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>LOC129217690</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>transforming growth factor-beta receptor-associated protein 1-like</t>
         </is>
       </c>
     </row>
@@ -7700,7 +10388,22 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t>LOC107451989</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t>microspherule protein 1</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>LOC129221325</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>microspherule protein 1-like</t>
         </is>
       </c>
     </row>
@@ -7742,7 +10445,22 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t>LOC107453087</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t>6-phosphogluconate dehydrogenase, decarboxylating isoform X2</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>LOC129225577</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>6-phosphogluconate dehydrogenase, decarboxylating-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -7787,6 +10505,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>LOC129226594</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>proteasome assembly chaperone 3-like</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7826,7 +10559,22 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t>LOC107450007</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t>mitochondrial cardiolipin hydrolase</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>LOC129226425</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129226425</t>
         </is>
       </c>
     </row>
@@ -7868,7 +10616,22 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t>LOC107440833</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t>transmembrane protein 199</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>LOC129220299</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>transmembrane protein 199-like</t>
         </is>
       </c>
     </row>
@@ -7910,7 +10673,22 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t>LOC107452137</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t>SRSF protein kinase 3</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>LOC129234251</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>SRSF protein kinase 3-like</t>
         </is>
       </c>
     </row>
@@ -7952,7 +10730,22 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t>LOC107441193</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t>ubiquitin-associated domain-containing protein 1</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>LOC129227466</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>ubiquitin-associated domain-containing protein 1-like</t>
         </is>
       </c>
     </row>
@@ -7994,7 +10787,22 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t>LOC107444205</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t>acyl-coenzyme A diphosphatase NUDT19 isoform X1</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>LOC129216090</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>acyl-coenzyme A diphosphatase NUDT19-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -8036,7 +10844,22 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t>LOC107445190</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t>large ribosomal subunit protein uL15m</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>LOC129234211</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>39S ribosomal protein L15, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -8078,7 +10901,22 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t>LOC107438929</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t>REST corepressor 3 isoform X2</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>LOC129224678</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>REST corepressor 3-like</t>
         </is>
       </c>
     </row>
@@ -8108,7 +10946,22 @@
       <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
+          <t>LOC107436681</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t>nucleolar protein 10</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>LOC129227413</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>nucleolar protein 10-like</t>
         </is>
       </c>
     </row>
@@ -8150,7 +11003,22 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t>LOC107448893</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t>probable splicing factor, arginine/serine-rich 5 isoform X2</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>LOC129221951</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>probable splicing factor, arginine/serine-rich 5</t>
         </is>
       </c>
     </row>
@@ -8192,7 +11060,22 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t>LOC107441100</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t>F-box only protein 21 isoform X2</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>LOC129230619</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>F-box only protein 21-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -8234,6 +11117,21 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t>LOC107453812</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>tRNA wybutosine-synthesizing protein 2 homolog</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>LOC129216785</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
           <t>tRNA wybutosine-synthesizing protein 2 homolog</t>
         </is>
       </c>
@@ -8276,7 +11174,22 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t>LOC107445363</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t>putative glutathione-specific gamma-glutamylcyclotransferase 2 isoform X2</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>LOC129222645</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>glutathione-specific gamma-glutamylcyclotransferase 1-like</t>
         </is>
       </c>
     </row>
@@ -8306,7 +11219,22 @@
       <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
+          <t>LOC107450651</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -8336,7 +11264,22 @@
       <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
+          <t>LOC122272156</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>LOC129226104</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129226104</t>
         </is>
       </c>
     </row>
@@ -8378,7 +11321,22 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t>LOC107438261</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>LOC129225934</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129225934</t>
         </is>
       </c>
     </row>
@@ -8420,7 +11378,22 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t>LOC107447770</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t>cullin-1 isoform X2</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>LOC129231362</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>cullin-1-like</t>
         </is>
       </c>
     </row>
@@ -8462,7 +11435,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t>LOC107445525</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t>protein LLP homolog isoform X3</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>LOC129224692</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>protein LLP homolog</t>
         </is>
       </c>
     </row>
@@ -8492,7 +11480,22 @@
       <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
+          <t>LOC107438675</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t>dimethylaniline monooxygenase [N-oxide-forming</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>LOC129216067</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>flavin-containing monooxygenase 5-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -8534,7 +11537,22 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t>LOC107439260</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 92</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>LOC129221157</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>GRIP and coiled-coil domain-containing protein 2-like</t>
         </is>
       </c>
     </row>
@@ -8576,7 +11594,22 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t>RYB</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t>YY1-associated factor 2 isoform X2</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>LOC129229836</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>YY1-associated factor 2-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -8618,7 +11651,22 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t>LOC107449846</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t>synaptosomal-associated protein 29</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>LOC129226374</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>synaptosomal-associated protein 29-like</t>
         </is>
       </c>
     </row>
@@ -8660,7 +11708,22 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t>LOC107451466</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t>dehydrogenase/reductase SDR family protein 7-like isoform X1</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>LOC129225978</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>dehydrogenase/reductase SDR family protein 7-like</t>
         </is>
       </c>
     </row>
@@ -8702,7 +11765,22 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t>LOC107454837</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t>fos-related antigen 1</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>LOC129221181</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>transcription factor kayak-like</t>
         </is>
       </c>
     </row>
@@ -8744,7 +11822,22 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t>LOC107447013</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t>ferry endosomal RAB5 effector complex subunit 3 isoform X1</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>LOC129222029</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>protein C12orf4 homolog</t>
         </is>
       </c>
     </row>
@@ -8786,7 +11879,22 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t>LOC107443547</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>LOC129218821</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>glutamate receptor-interacting protein 2-like</t>
         </is>
       </c>
     </row>
@@ -8828,7 +11936,22 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t>LOC107448822</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>LOC129223810</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129223810</t>
         </is>
       </c>
     </row>
@@ -8870,7 +11993,22 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t>LOC107443032</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t>thioredoxin reductase 1, cytoplasmic isoform X1</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>LOC129221501</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>thioredoxin reductase 1, cytoplasmic-like</t>
         </is>
       </c>
     </row>
@@ -8900,7 +12038,22 @@
       <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
+          <t>LOC107450749</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>LOC129216516</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>tigger transposable element-derived protein 4-like</t>
         </is>
       </c>
     </row>
@@ -8942,7 +12095,22 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t>LOC107449107</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t>coiled-coil domain-containing protein 91</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>LOC129220503</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>coiled-coil domain-containing protein 91-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -8984,7 +12152,22 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t>LOC107442424</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t>BTB/POZ domain-containing adapter for CUL3-mediated RhoA degradation protein 3</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>LOC129226549</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>BTB/POZ domain-containing adapter for CUL3-mediated RhoA degradation protein 3-like</t>
         </is>
       </c>
     </row>
@@ -9014,7 +12197,22 @@
       <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
+          <t>LOC107446092</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t>translin-associated protein X</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>LOC129232648</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>translin-associated protein X-like</t>
         </is>
       </c>
     </row>
@@ -9056,7 +12254,22 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t>LOC107457165</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t>sorting nexin-10A</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>LOC129218619</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>sorting nexin-10B-like</t>
         </is>
       </c>
     </row>
@@ -9098,7 +12311,22 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t>LOC107457448</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t>CCR4-NOT transcription complex subunit 3 isoform X2</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>LOC129216625</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>CCR4-NOT transcription complex subunit 3-like</t>
         </is>
       </c>
     </row>
@@ -9140,6 +12368,21 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t>LOC107438009</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>poly [ADP-ribose</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>LOC129224173</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
           <t>poly [ADP-ribose</t>
         </is>
       </c>
@@ -9182,7 +12425,22 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t>LOC107456404</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t>protein FAM133 isoform X2</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>LOC129220201</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>protein FAM133-like</t>
         </is>
       </c>
     </row>
@@ -9224,7 +12482,22 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t>LOC107451105</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t>peroxiredoxin-6</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>LOC129228262</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>peroxiredoxin-6-like</t>
         </is>
       </c>
     </row>
@@ -9266,7 +12539,22 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t>LOC107450230</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t>guanine nucleotide exchange factor MSS4</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>LOC129220982</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>guanine nucleotide exchange factor MSS4-like</t>
         </is>
       </c>
     </row>
@@ -9308,6 +12596,21 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t>LOC107442523</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>protein AAR2 homolog</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>LOC129227758</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
           <t>protein AAR2 homolog</t>
         </is>
       </c>
@@ -9350,6 +12653,21 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t>LOC107448329</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>beta-1,3-galactosyltransferase 6-like</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>LOC129229567</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
           <t>beta-1,3-galactosyltransferase 6-like</t>
         </is>
       </c>
@@ -9392,7 +12710,22 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t>LOC122270279</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t>UPAR/Ly6 domain-containing protein rtv</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>LOC129218672</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129218672</t>
         </is>
       </c>
     </row>
@@ -9434,7 +12767,22 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t>LOC107451883</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t>poly(A)-specific ribonuclease PARN isoform X1</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>LOC129220334</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>poly(A)-specific ribonuclease PARN-like</t>
         </is>
       </c>
     </row>
@@ -9476,7 +12824,22 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t>LOC107446220</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t>transcription factor Sox-14</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>LOC129216340</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>transcription factor Sox-21-B-like</t>
         </is>
       </c>
     </row>
@@ -9518,7 +12881,22 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t>LOC107447068</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t>short-chain dehydrogenase/reductase family 16C member 6</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>LOC129233167</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>17-beta-hydroxysteroid dehydrogenase 13-like</t>
         </is>
       </c>
     </row>
@@ -9560,7 +12938,22 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t>LOC107436425</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t>insulin-like growth factor 2 mRNA-binding protein 1 isoform X3</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>LOC129219891</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>insulin-like growth factor 2 mRNA-binding protein 1 isoform X2</t>
         </is>
       </c>
     </row>
@@ -9590,7 +12983,22 @@
       <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
+          <t>LOC107438912</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t>mucin-3B</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>LOC129224367</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224367</t>
         </is>
       </c>
     </row>
@@ -9620,7 +13028,22 @@
       <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
+          <t>LOC107454498</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t>peptidyl-prolyl cis-trans isomerase NIMA-interacting 4</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>LOC129229217</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>peptidyl-prolyl cis-trans isomerase NIMA-interacting 1-like</t>
         </is>
       </c>
     </row>
@@ -9662,7 +13085,22 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t>LOC107442359</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t>ras-related protein Rab-22A-like</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>LOC129231257</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129231257</t>
         </is>
       </c>
     </row>
@@ -9704,6 +13142,21 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t>LOC107449810</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>TIP41-like protein</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>LOC129219787</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
           <t>TIP41-like protein</t>
         </is>
       </c>
@@ -9746,7 +13199,22 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t>LOC107450143</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t>small RNA 2'-O-methyltransferase</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>LOC129234606</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>small RNA 2'-O-methyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -9776,7 +13244,22 @@
       <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
+          <t>LOC107439464</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t>uncharacterized aarF domain-containing protein kinase 5 isoform X5</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>LOC129224013</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>uncharacterized aarF domain-containing protein kinase 5-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -9818,7 +13301,22 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t>LOC107436762</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t>angiogenic factor with G patch and FHA domains 1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>LOC129224054</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>angiogenic factor with G patch and FHA domains 1-like</t>
         </is>
       </c>
     </row>
@@ -9860,7 +13358,22 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t>LOC107455134</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t>FAST kinase domain-containing protein 4</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>LOC129222084</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>FAST kinase domain-containing protein 4-like</t>
         </is>
       </c>
     </row>
@@ -9902,7 +13415,22 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t>LOC107454171</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t>akirin-2</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>LOC129225169</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>akirin-2-like</t>
         </is>
       </c>
     </row>
@@ -9944,7 +13472,22 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t>LOC107442147</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t>ion channel TACAN</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>LOC129222193</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>ion channel TACAN-like</t>
         </is>
       </c>
     </row>
@@ -9986,7 +13529,22 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t>LOC107448912</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>LOC129231201</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129231201</t>
         </is>
       </c>
     </row>
@@ -10028,7 +13586,22 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t>LOC107441438</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t>sorting nexin-5 isoform X1</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>LOC129229554</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>sorting nexin-32-like</t>
         </is>
       </c>
     </row>
@@ -10058,7 +13631,22 @@
       <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
+          <t>LOC139425704</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>LOC129217735</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129217735</t>
         </is>
       </c>
     </row>
@@ -10100,7 +13688,22 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t>LOC107454173</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t>atlastin-2</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>LOC129225082</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>atlastin-2-like</t>
         </is>
       </c>
     </row>
@@ -10127,22 +13730,37 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>129224060</t>
+          <t>129224059</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]; GO:0016853 [Name: isomerase activity]</t>
+          <t>GO:0016853 [Name: isomerase activity]; GO:0030246 [Name: carbohydrate binding]; GO:0005975 [Name: carbohydrate metabolic process]</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>uncharacterized LOC129224060</t>
+          <t>uncharacterized LOC129224059</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t>LOC107456148</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>LOC129224059</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224059</t>
         </is>
       </c>
     </row>
@@ -10184,7 +13802,22 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t>LOC107455563</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t>transmembrane emp24 domain-containing protein 10</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>LOC129228264</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>transmembrane emp24 domain-containing protein bai-like</t>
         </is>
       </c>
     </row>
@@ -10226,7 +13859,22 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t>LOC107452596</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t>myosin heavy chain, clone 203</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>LOC129226434</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>HAUS augmin-like complex subunit 4</t>
         </is>
       </c>
     </row>
@@ -10256,6 +13904,21 @@
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
+          <t>LOC107445466</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>peptide chain release factor 1-like, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>LOC129223820</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
           <t>peptide chain release factor 1-like, mitochondrial</t>
         </is>
       </c>
@@ -10298,7 +13961,22 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t>LOC107444249</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t>histone acetyltransferase type B catalytic subunit</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>LOC129222113</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>histone acetyltransferase type B catalytic subunit-like</t>
         </is>
       </c>
     </row>
@@ -10340,7 +14018,22 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t>LOC107442132</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t>glycine cleavage system H protein</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>LOC129229887</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>glycine cleavage system H protein-like</t>
         </is>
       </c>
     </row>
@@ -10370,7 +14063,22 @@
       <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
+          <t>LOC107455223</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t>ribosome biogenesis protein NOP53</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -10412,7 +14120,22 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t>LOC107437133</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t>J domain-containing protein</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>LOC129219762</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>J domain-containing protein-like</t>
         </is>
       </c>
     </row>
@@ -10454,7 +14177,22 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t>LOC107457130</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>LOC129226454</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129226454</t>
         </is>
       </c>
     </row>
@@ -10487,6 +14225,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10526,7 +14279,22 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t>LOC107456021</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t>SR-related and CTD-associated factor 4</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>LOC129225712</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>SR-related and CTD-associated factor 4-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -10568,7 +14336,22 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t>LOC107451788</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t>nondiscriminating glutamyl-tRNA synthetase EARS2, mitochondrial isoform X1</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>LOC129228500</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>probable glutamate--tRNA ligase, mitochondrial</t>
         </is>
       </c>
     </row>
@@ -10610,7 +14393,22 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t>LOC107437044</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t>B-cell receptor-associated protein 29 isoform X2</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>LOC129232688</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>B-cell receptor-associated protein 31-like</t>
         </is>
       </c>
     </row>
@@ -10652,7 +14450,22 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t>LOC107438486</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t>inositol monophosphatase 3</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>LOC129233272</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>inositol monophosphatase 3-like</t>
         </is>
       </c>
     </row>
@@ -10694,6 +14507,21 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t>LOC107455010</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>calcyphosin-like protein</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>LOC129233967</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
           <t>calcyphosin-like protein</t>
         </is>
       </c>
@@ -10736,7 +14564,22 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t>LOC107448297</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t>eukaryotic translation initiation factor 3 subunit K</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>LOC129234006</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>eukaryotic translation initiation factor 3 subunit K-like</t>
         </is>
       </c>
     </row>
@@ -10778,7 +14621,22 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t>LOC107442282</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t>dnaJ homolog subfamily B member 4</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>LOC129232248</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>dnaJ protein homolog 1-like</t>
         </is>
       </c>
     </row>
@@ -10820,7 +14678,22 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t>LOC107444720</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>LOC129232407</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129232407</t>
         </is>
       </c>
     </row>
@@ -10853,6 +14726,21 @@
           <t>NO_HIT</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10892,7 +14780,22 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t>LOC107438968</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t>protein ILRUN</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>LOC129227000</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: protein ILRUN-like</t>
         </is>
       </c>
     </row>
@@ -10934,6 +14837,21 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t>LOC107451986</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>T-box transcription factor TBX10-like</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>LOC129219897</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
           <t>T-box transcription factor TBX10-like</t>
         </is>
       </c>
@@ -10976,6 +14894,21 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t>LOC107438785</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>leukocyte receptor cluster member 1 homolog</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>LOC129226216</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
           <t>leukocyte receptor cluster member 1 homolog</t>
         </is>
       </c>
@@ -11018,7 +14951,22 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t>LOC107446319</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>LOC129228113</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129228113</t>
         </is>
       </c>
     </row>
@@ -11060,7 +15008,22 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
+          <t>LOC110282899</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t>UPF0449 protein C19orf25 homolog</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>LOC129234604</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129234604</t>
         </is>
       </c>
     </row>
@@ -11102,7 +15065,22 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
+          <t>LOC107453900</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
           <t>sn-1-specific diacylglycerol lipase ABHD11 isoform X1</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>LOC129223085</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>protein ABHD11-like</t>
         </is>
       </c>
     </row>
@@ -11144,7 +15122,22 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
+          <t>LOC107440473</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
           <t>AP-5 complex subunit beta-1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>LOC129228520</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>AP-5 complex subunit beta-1-like</t>
         </is>
       </c>
     </row>
@@ -11186,7 +15179,22 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
+          <t>LOC107456557</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
           <t>GPN-loop GTPase 3</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>LOC129227553</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>GPN-loop GTPase 3-like</t>
         </is>
       </c>
     </row>
@@ -11228,7 +15236,22 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
+          <t>LOC107443583</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
           <t>diphthine methyltransferase</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>LOC129229360</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>diphthine methyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -11270,7 +15293,22 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
+          <t>LOC107440076</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>LOC129224569</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224569</t>
         </is>
       </c>
     </row>
@@ -11300,7 +15338,22 @@
       <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
+          <t>LOC107438959</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
           <t>U1 small nuclear ribonucleoprotein 70 kDa</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>LOC129219708</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>U1 small nuclear ribonucleoprotein 70 kDa-like</t>
         </is>
       </c>
     </row>
@@ -11342,7 +15395,22 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
+          <t>LOC107452212</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
           <t>rRNA methyltransferase 1, mitochondrial isoform X2</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>LOC129225064</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>rRNA methyltransferase 1, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -11384,7 +15452,22 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
+          <t>LOC107442017</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>LOC129221300</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129221300</t>
         </is>
       </c>
     </row>
@@ -11425,6 +15508,21 @@
         </is>
       </c>
       <c r="J274" t="inlineStr">
+        <is>
+          <t>LOC107456850</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>ribosomal RNA processing protein 36 homolog</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>LOC129219842</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
         <is>
           <t>ribosomal RNA processing protein 36 homolog</t>
         </is>
@@ -11456,7 +15554,22 @@
       <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
+          <t>LOC107446700</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
           <t>RING finger protein 141</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>LOC129222583</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>E3 ubiquitin-protein ligase RNF8-like</t>
         </is>
       </c>
     </row>
@@ -11498,7 +15611,22 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
+          <t>LOC107437303</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
           <t>BTB/POZ domain-containing protein KCTD5</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>LOC129220523</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>BTB/POZ domain-containing protein KCTD5-like</t>
         </is>
       </c>
     </row>
@@ -11528,7 +15656,22 @@
       <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
+          <t>LOC107445056</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
           <t>equilibrative nucleoside transporter 3</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>LOC129227398</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: equilibrative nucleoside transporter 1-like</t>
         </is>
       </c>
     </row>
@@ -11570,7 +15713,22 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
+          <t>LOC107454355</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
           <t>protein lifeguard 1</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>LOC129217043</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>protein lifeguard 1-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -11612,7 +15770,22 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
+          <t>LOC107452555</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
           <t>zinc finger protein 91-like</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>LOC129226305</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>zinc finger protein 585B-like</t>
         </is>
       </c>
     </row>
@@ -11654,7 +15827,22 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
+          <t>LOC107449257</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
           <t>ufm1-specific protease 2 isoform X1</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>LOC129222207</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>ufm1-specific protease 2-like</t>
         </is>
       </c>
     </row>
@@ -11696,7 +15884,22 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
+          <t>LOC107457460</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t>inhibitor of growth protein 4</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>LOC129217547</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>inhibitor of growth protein 4-like</t>
         </is>
       </c>
     </row>
@@ -11738,7 +15941,22 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
+          <t>LOC107444488</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t>delta(3,5)-Delta(2,4)-dienoyl-CoA isomerase, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>LOC129217211</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>delta(3,5)-Delta(2,4)-dienoyl-CoA isomerase, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -11780,7 +15998,22 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
+          <t>LOC107442192</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
           <t>gastrula zinc finger protein XlCGF57.1</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>LOC129220967</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>zinc finger protein 708-like</t>
         </is>
       </c>
     </row>
@@ -11822,7 +16055,22 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
+          <t>LOC107455939</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
           <t>retinitis pigmentosa 9 protein</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>LOC129229667</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>retinitis pigmentosa 9 protein homolog</t>
         </is>
       </c>
     </row>
@@ -11864,7 +16112,22 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
+          <t>LOC107446292</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t>protein sel-1 homolog 1</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>LOC129225184</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>protein sel-1 homolog 1-like</t>
         </is>
       </c>
     </row>
@@ -11906,7 +16169,22 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
+          <t>LOC107448792</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t>uncharacterized protein MAL13P1.304 isoform X2</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>LOC129217757</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>cyanocobalamin reductase / alkylcobalamin dealkylase-like</t>
         </is>
       </c>
     </row>
@@ -11948,7 +16226,22 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
+          <t>LOC107456115</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
           <t>NSFL1 cofactor p47 isoform X1</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>LOC129221864</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>NSFL1 cofactor p47-like</t>
         </is>
       </c>
     </row>
@@ -11990,7 +16283,22 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
+          <t>LOC107452661</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t>ras-related protein Rab-30</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>LOC129223987</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>ras-related protein Rab-1D-like</t>
         </is>
       </c>
     </row>
@@ -12032,7 +16340,22 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
+          <t>LOC107436901</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
           <t>prohibitin 1</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>LOC129222013</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>prohibitin-2-like</t>
         </is>
       </c>
     </row>
@@ -12074,7 +16397,22 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
+          <t>LOC107436514</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
           <t>nuclear transcription factor Y subunit beta isoform X1</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>LOC129226103</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>nuclear transcription factor Y subunit beta-like</t>
         </is>
       </c>
     </row>
@@ -12116,7 +16454,22 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
+          <t>LOC107437146</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>LOC129224072</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129224072</t>
         </is>
       </c>
     </row>
@@ -12158,7 +16511,22 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
+          <t>LOC107456491</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
           <t>rRNA N(6)-adenosine-methyltransferase ZCCHC4 isoform X1</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>LOC129222293</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: rRNA N6-adenosine-methyltransferase ZCCHC4-like</t>
         </is>
       </c>
     </row>
@@ -12200,7 +16568,22 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
+          <t>LOC107456926</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t>tetraspanin-18B</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>LOC129230637</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>CD151 antigen-like</t>
         </is>
       </c>
     </row>
@@ -12242,7 +16625,22 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
+          <t>LOC107447010</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>LOC129217092</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129217092</t>
         </is>
       </c>
     </row>
@@ -12284,7 +16682,22 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
+          <t>LOC107454883</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t>exosome complex component RRP42</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>LOC129222186</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>exosome complex exonuclease RRP42-like</t>
         </is>
       </c>
     </row>
@@ -12326,7 +16739,22 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
+          <t>LOC107450832</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t>inositol-pentakisphosphate 2-kinase isoform X2</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>LOC129227271</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>inositol-pentakisphosphate 2-kinase-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -12368,7 +16796,22 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
+          <t>LOC107452708</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t>alpha-1,6-mannosyl-glycoprotein 2-beta-N-acetylglucosaminyltransferase</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>LOC129218349</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>alpha-1,6-mannosyl-glycoprotein 2-beta-N-acetylglucosaminyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -12410,7 +16853,22 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
+          <t>LOC107452659</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t>UTP--glucose-1-phosphate uridylyltransferase isoform X2</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>LOC129224124</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>UTP--glucose-1-phosphate uridylyltransferase-like</t>
         </is>
       </c>
     </row>
@@ -12440,7 +16898,22 @@
       <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
+          <t>LOC107450644</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
           <t>protein GUCD1 isoform X1</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>LOC129224508</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>protein GUCD1-like</t>
         </is>
       </c>
     </row>
@@ -12470,7 +16943,22 @@
       <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
+          <t>LOC107437348</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
           <t>TBC1 domain family member 30-like isoform X1</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>LOC129217744</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>TBC1 domain family member 30-like</t>
         </is>
       </c>
     </row>
@@ -12512,7 +17000,22 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
+          <t>LOC107437963</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>LOC129234392</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129234392</t>
         </is>
       </c>
     </row>
@@ -12542,7 +17045,22 @@
       <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
+          <t>LOC107447618</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
           <t>vinexin isoform X11</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>LOC129226623</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>sorbin and SH3 domain-containing protein 1-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -12584,6 +17102,21 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
+          <t>LOC107436710</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>leucine-rich repeat-containing protein 20-like</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>LOC129234480</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
           <t>leucine-rich repeat-containing protein 20-like</t>
         </is>
       </c>
@@ -12626,7 +17159,22 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
+          <t>LOC107454728</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
           <t>membrane progestin receptor gamma isoform X1</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>LOC129221858</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>membrane progestin receptor gamma-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -12668,7 +17216,22 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
+          <t>LOC107448447</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t>cytoplasmic dynein 2 light intermediate chain 1</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>LOC129220198</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>cytoplasmic dynein 2 light intermediate chain 1-like</t>
         </is>
       </c>
     </row>
@@ -12710,7 +17273,22 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
+          <t>LOC107438723</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t>zinc finger MYND domain-containing protein 19 isoform X2</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>LOC129222734</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>zinc finger MYND domain-containing protein 19-like</t>
         </is>
       </c>
     </row>
@@ -12752,7 +17330,22 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
+          <t>LOC107437927</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t>large ribosomal subunit protein mL62 isoform X2</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>LOC129229777</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>peptidyl-tRNA hydrolase ICT1, mitochondrial-like</t>
         </is>
       </c>
     </row>
@@ -12794,7 +17387,22 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
+          <t>LOC107443620</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t>G protein pathway suppressor 2</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>LOC129222006</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>G protein pathway suppressor 2-like</t>
         </is>
       </c>
     </row>
@@ -12824,7 +17432,22 @@
       <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
+          <t>LOC107441460</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t>trimeric intracellular cation channel type 1B.1</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>LOC129218500</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>trimeric intracellular cation channel type 1B.1-like</t>
         </is>
       </c>
     </row>
@@ -12854,6 +17477,21 @@
       <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
+          <t>LOC107456517</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>ras-related protein Rab-3</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>LOC129217689</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
           <t>ras-related protein Rab-3</t>
         </is>
       </c>
@@ -12896,7 +17534,22 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
+          <t>LOC107455388</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
           <t>snRNA-activating protein complex subunit 3</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>LOC129232963</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>snRNA-activating protein complex subunit 3-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -12938,7 +17591,22 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
+          <t>LOC107452995</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
           <t>transmembrane protein 230</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>LOC129231610</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>transmembrane protein 230-like</t>
         </is>
       </c>
     </row>
@@ -12980,6 +17648,21 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
+          <t>LOC122272793</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>dynactin subunit 3-like</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>LOC129227745</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
           <t>dynactin subunit 3-like</t>
         </is>
       </c>
@@ -13022,7 +17705,22 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
+          <t>LOC107437788</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
           <t>outer mitochondrial transmembrane helix translocase isoform X1</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>LOC129221963</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>outer mitochondrial transmembrane helix translocase-like</t>
         </is>
       </c>
     </row>
@@ -13064,7 +17762,22 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
+          <t>LOC107439364</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
           <t>AN1-type zinc finger protein 2A isoform X2</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>LOC129225295</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>AN1-type zinc finger protein 2A-like</t>
         </is>
       </c>
     </row>
@@ -13106,7 +17819,22 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
+          <t>LOC107449536</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>LOC129231471</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129231471</t>
         </is>
       </c>
     </row>
@@ -13148,7 +17876,22 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
+          <t>LOC107436193</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
           <t>dual serine/threonine and tyrosine protein kinase isoform X3</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>LOC129225656</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>dual serine/threonine and tyrosine protein kinase-like isoform X2</t>
         </is>
       </c>
     </row>
@@ -13190,6 +17933,21 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
+          <t>LOC107444407</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>NADH dehydrogenase [ubiquinone</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>LOC129228728</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
           <t>NADH dehydrogenase [ubiquinone</t>
         </is>
       </c>
@@ -13232,6 +17990,21 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
+          <t>LOC107456154</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>poly [ADP-ribose</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>LOC129225746</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
           <t>poly [ADP-ribose</t>
         </is>
       </c>
@@ -13259,12 +18032,12 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>129225077</t>
+          <t>129218840</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>GO:0000723 [Name: telomere maintenance]; GO:0005634 [Name: nucleus]</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -13274,7 +18047,22 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
+          <t>LOC107442904</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t>telomere-associated protein RIF1</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>LOC129225077</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>telomere-associated protein RIF1-like</t>
         </is>
       </c>
     </row>
@@ -13316,6 +18104,21 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
+          <t>LOC107450907</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>putative OPA3-like protein CG13603</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>LOC129224028</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
           <t>putative OPA3-like protein CG13603</t>
         </is>
       </c>
@@ -13358,6 +18161,21 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
+          <t>LOC107452913</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>RCC1-like G exchanging factor-like protein</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>LOC129223720</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
           <t>RCC1-like G exchanging factor-like protein</t>
         </is>
       </c>
@@ -13400,7 +18218,22 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
+          <t>LOC107447217</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
           <t>U3 small nucleolar RNA-associated protein NOL7</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>LOC129217319</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129217319</t>
         </is>
       </c>
     </row>
@@ -13442,7 +18275,22 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
+          <t>LOC107450060</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
           <t>armadillo repeat-containing protein 7 isoform X2</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>LOC129229294</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>armadillo repeat-containing protein 7-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -13484,7 +18332,22 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
+          <t>LOC107454988</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
           <t>polyadenylation and cleavage factor homolog 11 isoform X2</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>LOC129218287</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129218287</t>
         </is>
       </c>
     </row>
@@ -13526,7 +18389,22 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
+          <t>LOC122272154</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
           <t>mitochondrial protein C2orf69 homolog</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>LOC129225274</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>mitochondrial protein C2orf69-like</t>
         </is>
       </c>
     </row>
@@ -13556,7 +18434,22 @@
       <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
+          <t>LOC107456619</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
           <t>HIG1 domain family member 2A, mitochondrial</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>NO_HIT</t>
         </is>
       </c>
     </row>
@@ -13598,7 +18491,22 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
+          <t>LOC107456843</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
           <t>AH receptor-interacting protein isoform X2</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>LOC129233430</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>AH receptor-interacting protein-like isoform X1</t>
         </is>
       </c>
     </row>
@@ -13640,7 +18548,22 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
+          <t>LOC107446359</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
           <t>uncharacterized protein</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>LOC129222744</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>uncharacterized protein LOC129222744</t>
         </is>
       </c>
     </row>
@@ -13682,7 +18605,22 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
+          <t>LOC107441618</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
           <t>porphobilinogen deaminase isoform X1</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>LOC129226569</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>porphobilinogen deaminase-like</t>
         </is>
       </c>
     </row>
@@ -13724,7 +18662,22 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
+          <t>LOC107441975</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
           <t>soma ferritin</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>LOC129220427</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>soma ferritin-like</t>
         </is>
       </c>
     </row>
@@ -13766,7 +18719,22 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
+          <t>LOC107453531</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
           <t>sorting nexin-29</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>LOC129225777</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>sorting nexin-29-like</t>
         </is>
       </c>
     </row>
@@ -13808,6 +18776,21 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
+          <t>LOC107446087</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>ero1-like protein</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>LOC129232649</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
           <t>ero1-like protein</t>
         </is>
       </c>
@@ -13850,6 +18833,21 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
+          <t>LOC122271094</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>LOW QUALITY PROTEIN: thioredoxin reductase-like selenoprotein T homolog CG3887</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>LOC129230750</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
           <t>LOW QUALITY PROTEIN: thioredoxin reductase-like selenoprotein T homolog CG3887</t>
         </is>
       </c>
@@ -13892,7 +18890,22 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
+          <t>LOC107448937</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
           <t>U-scoloptoxin(19)-Tl1a isoform X1</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>LOC129231768</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>U-scoloptoxin(19)-Tl1a-like</t>
         </is>
       </c>
     </row>
@@ -13934,7 +18947,22 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
+          <t>LOC107444085</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
           <t>U11/U12 small nuclear ribonucleoprotein 25 kDa protein isoform X3</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>LOC129233683</t>
+        </is>
+      </c>
+      <c r="M336" t="inlineStr">
+        <is>
+          <t>U11/U12 small nuclear ribonucleoprotein 25 kDa protein-like</t>
         </is>
       </c>
     </row>
@@ -13976,7 +19004,22 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
+          <t>LOC107446798</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
           <t>uncharacterized protein isoform X1</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>LOC129217819</t>
+        </is>
+      </c>
+      <c r="M337" t="inlineStr">
+        <is>
+          <t>transmembrane protein 53-like</t>
         </is>
       </c>
     </row>
@@ -14018,7 +19061,22 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
+          <t>LOC107442742</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
           <t>mitochondrial import inner membrane translocase subunit TIM50-C isoform X1</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>LOC129222783</t>
+        </is>
+      </c>
+      <c r="M338" t="inlineStr">
+        <is>
+          <t>mitochondrial import inner membrane translocase subunit TIM50-like</t>
         </is>
       </c>
     </row>
